--- a/output/pdf_financials_xlsx/OCO.xlsx
+++ b/output/pdf_financials_xlsx/OCO.xlsx
@@ -6239,52 +6239,52 @@
         <v>0.327887</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.978698</v>
+        <v>0.990063</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.207252</v>
+        <v>1.222098</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.212448</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.626862</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.317979</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.110254</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.238582</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.293674</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.392571</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.758706</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.051282</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.62153</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>12.584865</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>15.304582</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>16.36951</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>18.273632</v>
       </c>
     </row>
     <row r="93">
@@ -7813,49 +7813,49 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.105382</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-5.617049</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>6.67159</v>
+        <v>5.855937</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.140294</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.041203</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.030352</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.042074</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.149129</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.5149359999999999</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-1.673323</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-5.179526</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-14.489283</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-23.662319</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-6.69233</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-5.187104</v>
       </c>
     </row>
     <row r="119">
@@ -10288,7 +10288,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11899,7 +11903,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -13008,7 +13016,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -13719,7 +13731,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -16761,7 +16777,11 @@
           <t>Reserves (Note 8) 2,626,862</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -18569,7 +18589,11 @@
           <t>RESERVES (Note 8)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -20661,7 +20685,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OCO.xlsx
+++ b/output/pdf_financials_xlsx/OCO.xlsx
@@ -1001,7 +1001,7 @@
         <v>1.102943</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.000628</v>
+        <v>2.653683</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>2.783918</v>
@@ -1130,31 +1130,31 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.004236</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000628</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.097578</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.126046</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.134579</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.041941</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.040621</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.07034799999999999</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -2200,31 +2200,31 @@
         <v>-1.063501</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.017824</v>
+        <v>-2.02206</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-9.368385999999999</v>
+        <v>-9.369014</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.66957</v>
+        <v>1.571992</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.961415</v>
+        <v>-2.087461</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.738962</v>
+        <v>-0.873541</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.155369</v>
+        <v>-0.19731</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-1.377241</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.546685</v>
+        <v>-1.587306</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.32683</v>
+        <v>0.256482</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2332,31 +2332,31 @@
         <v>-1.063501</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.012822</v>
+        <v>-2.017058</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-9.365157</v>
+        <v>-9.365785000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.672724</v>
+        <v>1.575146</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.958962</v>
+        <v>-2.085008</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.737033</v>
+        <v>-0.8716120000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.153835</v>
+        <v>-0.195776</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-1.376009</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.545684</v>
+        <v>-1.586305</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.327652</v>
+        <v>0.257304</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2642,55 +2642,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.051467</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.37623</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.558766</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.128011</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.059477</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.130322</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.419986</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.407127</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.373872</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.938804</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.488402</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.407226</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>20.213252</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>23.026889</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.456085</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.828999</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.169629</v>
       </c>
     </row>
     <row r="35">
@@ -2758,55 +2758,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.051467</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.37623</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.558766</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.128011</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.059477</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.130322</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.419986</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.407127</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.373872</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.5486</v>
+        <v>1.487404</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.401444</v>
+        <v>0.889846</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.215031</v>
+        <v>0.6222569999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.271044</v>
+        <v>20.484296</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.168038</v>
+        <v>23.194927</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.028006</v>
+        <v>1.484091</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.019604</v>
+        <v>0.848603</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.20159</v>
+        <v>0.371219</v>
       </c>
     </row>
     <row r="37">
@@ -3454,55 +3454,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.096583</v>
+        <v>0.045116</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.449121</v>
+        <v>0.072891</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.92335</v>
+        <v>0.364584</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.226573</v>
+        <v>0.098562</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.073934</v>
+        <v>0.014457</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.502295</v>
+        <v>1.371973</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.319709</v>
+        <v>2.899723</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.471308</v>
+        <v>1.064181</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.378787</v>
+        <v>0.004915</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.394215</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.101734</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.311083</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>20.644403</v>
+        <v>0.431151</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>23.461824</v>
+        <v>0.434935</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.988663</v>
+        <v>0.532578</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.221206</v>
+        <v>0.392207</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.301833</v>
+        <v>0.132204</v>
       </c>
     </row>
     <row r="49">
@@ -8227,7 +8227,7 @@
         <v>0</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.052129</v>
       </c>
     </row>
     <row r="125">
@@ -8289,7 +8289,7 @@
         <v>0</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.052129</v>
       </c>
     </row>
     <row r="126">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
@@ -21227,7 +21227,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -49068,7 +49072,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -50478,7 +50482,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -55803,7 +55807,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -58712,7 +58716,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -58736,10 +58740,10 @@
         </is>
       </c>
       <c r="I503" s="5" t="n">
-        <v>-2.653683</v>
+        <v>2.653683</v>
       </c>
       <c r="J503" s="5" t="n">
-        <v>-1.063537</v>
+        <v>1.063537</v>
       </c>
       <c r="K503" t="inlineStr">
         <is>
@@ -58916,7 +58920,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -60841,7 +60845,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -63172,7 +63176,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
